--- a/ci-cd-merge-resolver/repoCollector/datasets/feign.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/feign.xlsx
@@ -150,13 +150,13 @@
         <v>2.0</v>
       </c>
       <c r="G2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>40.969993591308594</v>
+        <v>37.084999084472656</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
